--- a/outputs/daily/hr_rankings_2026-08-23.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-23.xlsx
@@ -54927,27 +54927,27 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>679845</t>
+          <t>672569</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Nick Loftin</t>
+          <t>Gustavo Campero</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-08-23T18:10:00Z</t>
+          <t>2026-08-23T18:35:00Z</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -54957,14 +54957,26 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Cal Quantrill</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>615698</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L199" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="M199" t="inlineStr">
         <is>
@@ -54978,26 +54990,26 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P199" t="n">
-        <v>16.1</v>
+        <v>20.2</v>
       </c>
       <c r="Q199" t="n">
-        <v>41.2</v>
+        <v>44.7</v>
       </c>
       <c r="R199" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="S199" t="n">
-        <v>88.7</v>
+        <v>47.9</v>
       </c>
       <c r="T199" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U199" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="V199" t="inlineStr">
         <is>
@@ -55011,7 +55023,7 @@
       </c>
       <c r="X199" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y199" t="inlineStr">
@@ -55036,7 +55048,7 @@
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD199" t="inlineStr"/>
@@ -55048,17 +55060,17 @@
       </c>
       <c r="AG199" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI199" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AJ199" t="inlineStr">
@@ -55068,95 +55080,119 @@
       </c>
       <c r="AK199" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/20, 0 HR</t>
+          <t>Contact streak: 1/3 over last 1 games</t>
         </is>
       </c>
       <c r="AL199" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.0% barrel, 12.9 HR allowed</t>
         </is>
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN199" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>29.87</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>87.29</t>
+          <t>92.65</t>
         </is>
       </c>
       <c r="AQ199" t="inlineStr">
         <is>
-          <t>96.833</t>
+          <t>101.3103</t>
         </is>
       </c>
       <c r="AR199" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>0.2821</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr">
         <is>
-          <t>0.1137</t>
+          <t>0.0666</t>
         </is>
       </c>
       <c r="AT199" t="inlineStr">
         <is>
-          <t>0.2989</t>
+          <t>0.2326</t>
         </is>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>69.12</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>44.71</t>
+          <t>44.54</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>0.1434</t>
-        </is>
-      </c>
-      <c r="BA199" t="inlineStr"/>
-      <c r="BB199" t="inlineStr"/>
-      <c r="BC199" t="inlineStr"/>
-      <c r="BD199" t="inlineStr"/>
-      <c r="BE199" t="inlineStr"/>
-      <c r="BF199" t="inlineStr"/>
+          <t>0.0519</t>
+        </is>
+      </c>
+      <c r="BA199" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="BB199" t="inlineStr">
+        <is>
+          <t>37.37</t>
+        </is>
+      </c>
+      <c r="BC199" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="BD199" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="BE199" t="inlineStr">
+        <is>
+          <t>0.1835</t>
+        </is>
+      </c>
+      <c r="BF199" t="inlineStr">
+        <is>
+          <t>29.01</t>
+        </is>
+      </c>
       <c r="BG199" t="inlineStr"/>
       <c r="BH199" t="inlineStr"/>
       <c r="BI199" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ199" t="inlineStr"/>
@@ -55167,22 +55203,22 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>622268</t>
+          <t>679845</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Donovan Walton</t>
+          <t>Nick Loftin</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -55197,26 +55233,14 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>Cristian Javier</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>664299</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
       <c r="L200" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="M200" t="inlineStr">
         <is>
@@ -55230,26 +55254,26 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P200" t="n">
         <v>16.1</v>
       </c>
       <c r="Q200" t="n">
-        <v>43.8</v>
+        <v>41.2</v>
       </c>
       <c r="R200" t="n">
-        <v>27.6</v>
+        <v>23.2</v>
       </c>
       <c r="S200" t="n">
-        <v>47.9</v>
+        <v>88.7</v>
       </c>
       <c r="T200" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U200" t="n">
-        <v>50.3</v>
+        <v>0</v>
       </c>
       <c r="V200" t="inlineStr">
         <is>
@@ -55263,7 +55287,7 @@
       </c>
       <c r="X200" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y200" t="inlineStr">
@@ -55288,7 +55312,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD200" t="inlineStr"/>
@@ -55305,134 +55329,110 @@
       </c>
       <c r="AH200" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI200" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
         <is>
-          <t>Contact streak: 6/18 over last 7 games</t>
+          <t>Last 7 games: 2/20, 0 HR</t>
         </is>
       </c>
       <c r="AL200" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.9% barrel, 5.8 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN200" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>34.98</t>
+          <t>29.87</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>89.17</t>
+          <t>87.29</t>
         </is>
       </c>
       <c r="AQ200" t="inlineStr">
         <is>
-          <t>97.7845</t>
+          <t>96.833</t>
         </is>
       </c>
       <c r="AR200" t="inlineStr">
         <is>
-          <t>0.3625</t>
+          <t>0.345</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr">
         <is>
-          <t>0.1026</t>
+          <t>0.1137</t>
         </is>
       </c>
       <c r="AT200" t="inlineStr">
         <is>
-          <t>0.3062</t>
+          <t>0.2989</t>
         </is>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>67.71</t>
+          <t>69.12</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>37.07</t>
+          <t>44.71</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>0.1197</t>
-        </is>
-      </c>
-      <c r="BA200" t="inlineStr">
-        <is>
-          <t>7.9</t>
-        </is>
-      </c>
-      <c r="BB200" t="inlineStr">
-        <is>
-          <t>38.16</t>
-        </is>
-      </c>
-      <c r="BC200" t="inlineStr">
-        <is>
-          <t>89.81</t>
-        </is>
-      </c>
-      <c r="BD200" t="inlineStr">
-        <is>
-          <t>0.4229</t>
-        </is>
-      </c>
-      <c r="BE200" t="inlineStr">
-        <is>
-          <t>0.1663</t>
-        </is>
-      </c>
-      <c r="BF200" t="inlineStr">
-        <is>
-          <t>38.59</t>
-        </is>
-      </c>
+          <t>0.1434</t>
+        </is>
+      </c>
+      <c r="BA200" t="inlineStr"/>
+      <c r="BB200" t="inlineStr"/>
+      <c r="BC200" t="inlineStr"/>
+      <c r="BD200" t="inlineStr"/>
+      <c r="BE200" t="inlineStr"/>
+      <c r="BF200" t="inlineStr"/>
       <c r="BG200" t="inlineStr"/>
       <c r="BH200" t="inlineStr"/>
       <c r="BI200" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ200" t="inlineStr"/>
@@ -55443,27 +55443,27 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>672569</t>
+          <t>622268</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Gustavo Campero</t>
+          <t>Donovan Walton</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-08-23T18:35:00Z</t>
+          <t>2026-08-23T18:10:00Z</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -55478,12 +55478,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Cal Quantrill</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>615698</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -55510,10 +55510,10 @@
         </is>
       </c>
       <c r="P201" t="n">
-        <v>19.6</v>
+        <v>16.1</v>
       </c>
       <c r="Q201" t="n">
-        <v>44.7</v>
+        <v>43.8</v>
       </c>
       <c r="R201" t="n">
         <v>27.6</v>
@@ -55522,10 +55522,10 @@
         <v>47.9</v>
       </c>
       <c r="T201" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U201" t="n">
-        <v>32</v>
+        <v>50.3</v>
       </c>
       <c r="V201" t="inlineStr">
         <is>
@@ -55564,7 +55564,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>H:2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD201" t="inlineStr"/>
@@ -55576,139 +55576,139 @@
       </c>
       <c r="AG201" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH201" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI201" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ201" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK201" t="inlineStr">
         <is>
-          <t>Contact streak: 1/3 over last 1 games</t>
+          <t>Contact streak: 6/18 over last 7 games</t>
         </is>
       </c>
       <c r="AL201" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 12.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.9% barrel, 5.8 HR allowed</t>
         </is>
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN201" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>34.98</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>89.17</t>
         </is>
       </c>
       <c r="AQ201" t="inlineStr">
         <is>
-          <t>95.8205</t>
+          <t>97.7845</t>
         </is>
       </c>
       <c r="AR201" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>0.3625</t>
         </is>
       </c>
       <c r="AS201" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>0.1026</t>
         </is>
       </c>
       <c r="AT201" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.3062</t>
         </is>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>67.71</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>37.07</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.1197</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>38.16</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="BD201" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.4229</t>
         </is>
       </c>
       <c r="BE201" t="inlineStr">
         <is>
-          <t>0.1835</t>
+          <t>0.1663</t>
         </is>
       </c>
       <c r="BF201" t="inlineStr">
         <is>
-          <t>29.01</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="BG201" t="inlineStr"/>
       <c r="BH201" t="inlineStr"/>
       <c r="BI201" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ201" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-08-23.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-23.xlsx
@@ -56787,27 +56787,27 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>677870</t>
+          <t>650859</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Leo Jimenez</t>
+          <t>Luis Rengifo</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-08-23T17:40:00Z</t>
+          <t>2026-08-23T20:10:00Z</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -56817,26 +56817,26 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Jackson Kent</t>
+          <t>Bailey Ober</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>800600</t>
+          <t>641927</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L206" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="M206" t="inlineStr">
         <is>
@@ -56854,22 +56854,22 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>28.7</v>
+        <v>15.9</v>
       </c>
       <c r="Q206" t="n">
-        <v>32.5</v>
+        <v>52.6</v>
       </c>
       <c r="R206" t="n">
-        <v>21.5</v>
+        <v>22.6</v>
       </c>
       <c r="S206" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T206" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U206" t="n">
-        <v>0.8</v>
+        <v>46.5</v>
       </c>
       <c r="V206" t="inlineStr">
         <is>
@@ -56883,7 +56883,7 @@
       </c>
       <c r="X206" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y206" t="inlineStr">
@@ -56908,7 +56908,7 @@
       </c>
       <c r="AC206" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD206" t="inlineStr"/>
@@ -56925,134 +56925,134 @@
       </c>
       <c r="AH206" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI206" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL206" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.2% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 10.3% barrel, 20.9 HR allowed</t>
         </is>
       </c>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN206" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>45.52</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>91.16</t>
+          <t>87.45</t>
         </is>
       </c>
       <c r="AQ206" t="inlineStr">
         <is>
-          <t>100.5261</t>
+          <t>97.7452</t>
         </is>
       </c>
       <c r="AR206" t="inlineStr">
         <is>
-          <t>0.3315</t>
+          <t>0.3561</t>
         </is>
       </c>
       <c r="AS206" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="AT206" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.3055</t>
         </is>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>70.76</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>13.57</t>
+          <t>14.09</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>35.42</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>17.87</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>0.0778</t>
+          <t>0.0837</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>36.58</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="BD206" t="inlineStr">
         <is>
-          <t>0.412</t>
+          <t>0.4655</t>
         </is>
       </c>
       <c r="BE206" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.2119</t>
         </is>
       </c>
       <c r="BF206" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>31.69</t>
         </is>
       </c>
       <c r="BG206" t="inlineStr"/>
       <c r="BH206" t="inlineStr"/>
       <c r="BI206" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ206" t="inlineStr"/>
@@ -57063,27 +57063,27 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>673237</t>
+          <t>677870</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>Leo Jimenez</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-08-23T18:10:00Z</t>
+          <t>2026-08-23T17:40:00Z</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -57098,12 +57098,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Brady Basso</t>
+          <t>Jackson Kent</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>669620</t>
+          <t>800600</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -57112,7 +57112,7 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="M207" t="inlineStr">
         <is>
@@ -57130,13 +57130,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="Q207" t="n">
-        <v>23.4</v>
+        <v>32.5</v>
       </c>
       <c r="R207" t="n">
-        <v>27.6</v>
+        <v>21.5</v>
       </c>
       <c r="S207" t="n">
         <v>59.8</v>
@@ -57145,7 +57145,7 @@
         <v>78</v>
       </c>
       <c r="U207" t="n">
-        <v>23.7</v>
+        <v>0.8</v>
       </c>
       <c r="V207" t="inlineStr">
         <is>
@@ -57184,7 +57184,7 @@
       </c>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD207" t="inlineStr"/>
@@ -57201,12 +57201,12 @@
       </c>
       <c r="AH207" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI207" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ207" t="inlineStr">
@@ -57216,12 +57216,12 @@
       </c>
       <c r="AK207" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AL207" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.3% barrel, 1.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.2% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM207" t="inlineStr">
@@ -57231,104 +57231,104 @@
       </c>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>37.23</t>
+          <t>45.52</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>91.16</t>
         </is>
       </c>
       <c r="AQ207" t="inlineStr">
         <is>
-          <t>99.4562</t>
+          <t>100.5261</t>
         </is>
       </c>
       <c r="AR207" t="inlineStr">
         <is>
-          <t>0.4188</t>
+          <t>0.3315</t>
         </is>
       </c>
       <c r="AS207" t="inlineStr">
         <is>
-          <t>0.1515</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="AT207" t="inlineStr">
         <is>
-          <t>0.3099</t>
+          <t>0.2904</t>
         </is>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>13.57</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>36.63</t>
+          <t>35.42</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>0.1456</t>
+          <t>0.0778</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="BD207" t="inlineStr">
         <is>
-          <t>0.3571</t>
+          <t>0.412</t>
         </is>
       </c>
       <c r="BE207" t="inlineStr">
         <is>
-          <t>0.0937</t>
+          <t>0.129</t>
         </is>
       </c>
       <c r="BF207" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="BG207" t="inlineStr"/>
       <c r="BH207" t="inlineStr"/>
       <c r="BI207" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ207" t="inlineStr"/>
@@ -57339,27 +57339,27 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>686797</t>
+          <t>673237</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-08-23T20:10:00Z</t>
+          <t>2026-08-23T18:10:00Z</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -57369,22 +57369,22 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Brady Basso</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>669620</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L208" t="n">
@@ -57406,22 +57406,22 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>19.2</v>
+        <v>28.6</v>
       </c>
       <c r="Q208" t="n">
-        <v>39.9</v>
+        <v>23.4</v>
       </c>
       <c r="R208" t="n">
-        <v>22.6</v>
+        <v>27.6</v>
       </c>
       <c r="S208" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T208" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U208" t="n">
-        <v>60.7</v>
+        <v>23.7</v>
       </c>
       <c r="V208" t="inlineStr">
         <is>
@@ -57435,7 +57435,7 @@
       </c>
       <c r="X208" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y208" t="inlineStr">
@@ -57477,27 +57477,27 @@
       </c>
       <c r="AH208" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI208" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL208" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.5% barrel, 16.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.3% barrel, 1.4 HR allowed</t>
         </is>
       </c>
       <c r="AM208" t="inlineStr">
@@ -57507,104 +57507,104 @@
       </c>
       <c r="AN208" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>37.23</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>88.11</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AQ208" t="inlineStr">
         <is>
-          <t>97.5423</t>
+          <t>99.4562</t>
         </is>
       </c>
       <c r="AR208" t="inlineStr">
         <is>
-          <t>0.3446</t>
+          <t>0.4188</t>
         </is>
       </c>
       <c r="AS208" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.1515</t>
         </is>
       </c>
       <c r="AT208" t="inlineStr">
         <is>
-          <t>0.2771</t>
+          <t>0.3099</t>
         </is>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>69.85</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>8.21</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>42.13</t>
+          <t>36.63</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>0.1669</t>
+          <t>0.1456</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>38.57</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="BD208" t="inlineStr">
         <is>
-          <t>0.4129</t>
+          <t>0.3571</t>
         </is>
       </c>
       <c r="BE208" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.0937</t>
         </is>
       </c>
       <c r="BF208" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="BG208" t="inlineStr"/>
       <c r="BH208" t="inlineStr"/>
       <c r="BI208" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ208" t="inlineStr"/>
@@ -57615,27 +57615,27 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>686797</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-08-23T17:35:00Z</t>
+          <t>2026-08-23T20:10:00Z</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -57645,17 +57645,17 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Shane Baz</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>669358</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -57664,7 +57664,7 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="M209" t="inlineStr">
         <is>
@@ -57682,22 +57682,22 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>15</v>
+        <v>19.2</v>
       </c>
       <c r="Q209" t="n">
-        <v>41.2</v>
+        <v>39.9</v>
       </c>
       <c r="R209" t="n">
-        <v>32.1</v>
+        <v>22.6</v>
       </c>
       <c r="S209" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T209" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U209" t="n">
-        <v>9.300000000000001</v>
+        <v>60.7</v>
       </c>
       <c r="V209" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
       </c>
       <c r="X209" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y209" t="inlineStr">
@@ -57753,27 +57753,27 @@
       </c>
       <c r="AH209" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI209" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL209" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 15.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.5% barrel, 16.4 HR allowed</t>
         </is>
       </c>
       <c r="AM209" t="inlineStr">
@@ -57783,104 +57783,104 @@
       </c>
       <c r="AN209" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>33.04</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>87.45</t>
+          <t>88.11</t>
         </is>
       </c>
       <c r="AQ209" t="inlineStr">
         <is>
-          <t>97.0954</t>
+          <t>97.5423</t>
         </is>
       </c>
       <c r="AR209" t="inlineStr">
         <is>
-          <t>0.3688</t>
+          <t>0.3446</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr">
         <is>
-          <t>0.1004</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="AT209" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2771</t>
         </is>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>68.77</t>
+          <t>69.85</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>8.21</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>35.62</t>
+          <t>42.13</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>21.12</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>0.1148</t>
+          <t>0.1669</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>38.57</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>90.05</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="BD209" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>0.4129</t>
         </is>
       </c>
       <c r="BE209" t="inlineStr">
         <is>
-          <t>0.1476</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="BF209" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="BG209" t="inlineStr"/>
       <c r="BH209" t="inlineStr"/>
       <c r="BI209" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ209" t="inlineStr"/>
@@ -57891,12 +57891,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>656775</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Cedric Mullins</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -57921,7 +57921,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -57958,7 +57958,7 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Q210" t="n">
         <v>41.2</v>
@@ -57967,13 +57967,13 @@
         <v>32.1</v>
       </c>
       <c r="S210" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T210" t="n">
         <v>80</v>
       </c>
       <c r="U210" t="n">
-        <v>10.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V210" t="inlineStr">
         <is>
@@ -57987,7 +57987,7 @@
       </c>
       <c r="X210" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y210" t="inlineStr">
@@ -58034,7 +58034,7 @@
       </c>
       <c r="AI210" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ210" t="inlineStr">
@@ -58044,7 +58044,7 @@
       </c>
       <c r="AK210" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL210" t="inlineStr">
@@ -58059,67 +58059,67 @@
       </c>
       <c r="AN210" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>32.89</t>
+          <t>33.04</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>88.03</t>
+          <t>87.45</t>
         </is>
       </c>
       <c r="AQ210" t="inlineStr">
         <is>
-          <t>97.8453</t>
+          <t>97.0954</t>
         </is>
       </c>
       <c r="AR210" t="inlineStr">
         <is>
-          <t>0.3176</t>
+          <t>0.3688</t>
         </is>
       </c>
       <c r="AS210" t="inlineStr">
         <is>
-          <t>0.1246</t>
+          <t>0.1004</t>
         </is>
       </c>
       <c r="AT210" t="inlineStr">
         <is>
-          <t>0.2679</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>70.89</t>
+          <t>68.77</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>35.62</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>32.01</t>
+          <t>21.12</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>0.1561</t>
+          <t>0.1148</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
@@ -58167,27 +58167,27 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>650859</t>
+          <t>656775</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Luis Rengifo</t>
+          <t>Cedric Mullins</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-08-23T20:10:00Z</t>
+          <t>2026-08-23T17:35:00Z</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -58197,17 +58197,17 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Bailey Ober</t>
+          <t>Shane Baz</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>641927</t>
+          <t>669358</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -58234,22 +58234,22 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>15.9</v>
+        <v>20</v>
       </c>
       <c r="Q211" t="n">
-        <v>52.6</v>
+        <v>41.2</v>
       </c>
       <c r="R211" t="n">
-        <v>22.6</v>
+        <v>32.1</v>
       </c>
       <c r="S211" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T211" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U211" t="n">
-        <v>40.7</v>
+        <v>10.6</v>
       </c>
       <c r="V211" t="inlineStr">
         <is>
@@ -58263,7 +58263,7 @@
       </c>
       <c r="X211" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y211" t="inlineStr">
@@ -58305,134 +58305,134 @@
       </c>
       <c r="AH211" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI211" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 1 HR</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AL211" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.3% barrel, 20.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN211" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>32.89</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>87.45</t>
+          <t>88.03</t>
         </is>
       </c>
       <c r="AQ211" t="inlineStr">
         <is>
-          <t>97.7452</t>
+          <t>97.8453</t>
         </is>
       </c>
       <c r="AR211" t="inlineStr">
         <is>
-          <t>0.3561</t>
+          <t>0.3176</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1246</t>
         </is>
       </c>
       <c r="AT211" t="inlineStr">
         <is>
-          <t>0.3055</t>
+          <t>0.2679</t>
         </is>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>70.76</t>
+          <t>70.89</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>17.87</t>
+          <t>32.01</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>0.0837</t>
+          <t>0.1561</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>36.58</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>90.05</t>
         </is>
       </c>
       <c r="BD211" t="inlineStr">
         <is>
-          <t>0.4655</t>
+          <t>0.393</t>
         </is>
       </c>
       <c r="BE211" t="inlineStr">
         <is>
-          <t>0.2119</t>
+          <t>0.1476</t>
         </is>
       </c>
       <c r="BF211" t="inlineStr">
         <is>
-          <t>31.69</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="BG211" t="inlineStr"/>
       <c r="BH211" t="inlineStr"/>
       <c r="BI211" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ211" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-08-23.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-23.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>63.1</v>
+        <v>63.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>40.1</v>
       </c>
       <c r="R2" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -826,34 +826,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1003,7 +999,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1068,11 +1064,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>59.6</v>
+        <v>60.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1092,7 +1088,7 @@
         <v>35.9</v>
       </c>
       <c r="R3" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -1110,34 +1106,30 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -1287,7 +1279,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1352,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>57.9</v>
+        <v>58.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1376,7 +1368,7 @@
         <v>35.9</v>
       </c>
       <c r="R4" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1394,34 +1386,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -1571,7 +1559,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1636,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>54.9</v>
+        <v>55.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1660,7 +1648,7 @@
         <v>40.1</v>
       </c>
       <c r="R5" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -1678,34 +1666,30 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1855,7 +1839,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1920,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>54.5</v>
+        <v>55</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1944,7 +1928,7 @@
         <v>35.9</v>
       </c>
       <c r="R6" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S6" t="n">
         <v>86.40000000000001</v>
@@ -1962,34 +1946,30 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2139,7 +2119,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2204,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>52.7</v>
+        <v>53.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2228,7 +2208,7 @@
         <v>35.9</v>
       </c>
       <c r="R7" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S7" t="n">
         <v>93.2</v>
@@ -2246,34 +2226,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2423,7 +2399,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2488,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>52.5</v>
+        <v>53.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2512,7 +2488,7 @@
         <v>40.1</v>
       </c>
       <c r="R8" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>96.59999999999999</v>
@@ -2530,34 +2506,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2707,7 +2679,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2772,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.3</v>
+        <v>52.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2796,7 +2768,7 @@
         <v>40.1</v>
       </c>
       <c r="R9" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -2814,34 +2786,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2991,7 +2959,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3056,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52.2</v>
+        <v>52.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3080,7 +3048,7 @@
         <v>40.1</v>
       </c>
       <c r="R10" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>52.4</v>
@@ -3098,34 +3066,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3275,7 +3239,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3340,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>51</v>
+        <v>51.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3364,7 +3328,7 @@
         <v>40.1</v>
       </c>
       <c r="R11" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -3382,34 +3346,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3559,7 +3519,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3624,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>50.4</v>
+        <v>50.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3648,7 +3608,7 @@
         <v>35.9</v>
       </c>
       <c r="R12" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S12" t="n">
         <v>52.4</v>
@@ -3666,34 +3626,30 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3843,7 +3799,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3908,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>48.6</v>
+        <v>49.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3932,7 +3888,7 @@
         <v>40.1</v>
       </c>
       <c r="R13" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -3950,34 +3906,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4127,7 +4079,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4192,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>45.9</v>
+        <v>46.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4216,7 +4168,7 @@
         <v>35.9</v>
       </c>
       <c r="R14" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S14" t="n">
         <v>76.2</v>
@@ -4234,34 +4186,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4411,7 +4359,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4476,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44</v>
+        <v>44.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4500,7 +4448,7 @@
         <v>35</v>
       </c>
       <c r="R15" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S15" t="n">
         <v>94.90000000000001</v>
@@ -4518,34 +4466,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4695,7 +4639,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4760,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4784,7 +4728,7 @@
         <v>40.1</v>
       </c>
       <c r="R16" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -4800,28 +4744,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4971,7 +4919,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -5036,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>39.1</v>
+        <v>39.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5060,7 +5008,7 @@
         <v>35.9</v>
       </c>
       <c r="R17" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S17" t="n">
         <v>64.3</v>
@@ -5078,34 +5026,30 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5255,7 +5199,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5320,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5344,7 +5288,7 @@
         <v>40.1</v>
       </c>
       <c r="R18" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -5362,34 +5306,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5539,7 +5479,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5604,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.2</v>
+        <v>35.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5628,7 +5568,7 @@
         <v>35.9</v>
       </c>
       <c r="R19" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -5646,34 +5586,30 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5823,7 +5759,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6214,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>63.1</v>
+        <v>63.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6238,7 +6174,7 @@
         <v>40.1</v>
       </c>
       <c r="R2" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -6256,34 +6192,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6433,7 +6365,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6498,11 +6430,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>59.6</v>
+        <v>60.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -6522,7 +6454,7 @@
         <v>35.9</v>
       </c>
       <c r="R3" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -6540,34 +6472,30 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -6717,7 +6645,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -6782,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>57.9</v>
+        <v>58.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6806,7 +6734,7 @@
         <v>35.9</v>
       </c>
       <c r="R4" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -6824,34 +6752,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7001,7 +6925,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -7066,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>54.9</v>
+        <v>55.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7090,7 +7014,7 @@
         <v>40.1</v>
       </c>
       <c r="R5" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -7108,34 +7032,30 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7285,7 +7205,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7350,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>54.5</v>
+        <v>55</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7374,7 +7294,7 @@
         <v>35.9</v>
       </c>
       <c r="R6" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S6" t="n">
         <v>86.40000000000001</v>
@@ -7392,34 +7312,30 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7569,7 +7485,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7634,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>52.7</v>
+        <v>53.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7658,7 +7574,7 @@
         <v>35.9</v>
       </c>
       <c r="R7" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S7" t="n">
         <v>93.2</v>
@@ -7676,34 +7592,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7853,7 +7765,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -7918,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>52.5</v>
+        <v>53.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7942,7 +7854,7 @@
         <v>40.1</v>
       </c>
       <c r="R8" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>96.59999999999999</v>
@@ -7960,34 +7872,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8137,7 +8045,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8202,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.3</v>
+        <v>52.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8226,7 +8134,7 @@
         <v>40.1</v>
       </c>
       <c r="R9" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -8244,34 +8152,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8421,7 +8325,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8486,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52.2</v>
+        <v>52.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8510,7 +8414,7 @@
         <v>40.1</v>
       </c>
       <c r="R10" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>52.4</v>
@@ -8528,34 +8432,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8705,7 +8605,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -8770,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>51</v>
+        <v>51.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8794,7 +8694,7 @@
         <v>40.1</v>
       </c>
       <c r="R11" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -8812,34 +8712,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8989,7 +8885,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -9054,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>50.4</v>
+        <v>50.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9078,7 +8974,7 @@
         <v>35.9</v>
       </c>
       <c r="R12" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S12" t="n">
         <v>52.4</v>
@@ -9096,34 +8992,30 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9273,7 +9165,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9338,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>48.6</v>
+        <v>49.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9362,7 +9254,7 @@
         <v>40.1</v>
       </c>
       <c r="R13" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -9380,34 +9272,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9557,7 +9445,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -9622,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>45.9</v>
+        <v>46.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9646,7 +9534,7 @@
         <v>35.9</v>
       </c>
       <c r="R14" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S14" t="n">
         <v>76.2</v>
@@ -9664,34 +9552,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9841,7 +9725,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -9906,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44</v>
+        <v>44.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9930,7 +9814,7 @@
         <v>35</v>
       </c>
       <c r="R15" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S15" t="n">
         <v>94.90000000000001</v>
@@ -9948,34 +9832,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10125,7 +10005,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10190,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10214,7 +10094,7 @@
         <v>40.1</v>
       </c>
       <c r="R16" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -10230,28 +10110,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10401,7 +10285,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10466,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>39.1</v>
+        <v>39.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10490,7 +10374,7 @@
         <v>35.9</v>
       </c>
       <c r="R17" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S17" t="n">
         <v>64.3</v>
@@ -10508,34 +10392,30 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10685,7 +10565,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -10750,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10774,7 +10654,7 @@
         <v>40.1</v>
       </c>
       <c r="R18" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -10792,34 +10672,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10969,7 +10845,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -11034,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.2</v>
+        <v>35.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -11058,7 +10934,7 @@
         <v>35.9</v>
       </c>
       <c r="R19" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -11076,34 +10952,30 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -11253,7 +11125,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-23.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-23.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
